--- a/1_Data/Navon_2021_psyarxiv/Exp3/CodeBook_Navon_2021_psyarxiv_Exp3_Clean.xlsx
+++ b/1_Data/Navon_2021_psyarxiv/Exp3/CodeBook_Navon_2021_psyarxiv_Exp3_Clean.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,29 +463,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>self-matching</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Trial</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -529,73 +529,73 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Matching</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Matching task performed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Matching;Nomatching</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Shape</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>self-matching</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Numerical</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Matching</t>
+          <t>Shape_Origin_Identity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Matching task performed</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Matching;Nomatching</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Numerical</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Label_Origin_Identity</t>
+          <t>Shape_English_Identity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Label_English_Identity</t>
+          <t>Shape_Standardized_Identity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Label_Standardized_Identity</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shape_Origin_Identity</t>
+          <t>Label_Origin_Identity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shape_English_Identity</t>
+          <t>Label_English_Identity</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shape_Standardized_Identity</t>
+          <t>Label_Standardized_Identity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,17 +727,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>CorrResponse</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Participant's response</t>
+          <t>Correct response key for the trial (as designed; from raw CRESP/CorrectAnswer)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>m;z</t>
+          <t>See per-study key mapping</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -749,34 +749,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RT_ms</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reaction time in milliseconds</t>
+          <t>Participant's response</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>m;z</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RT_sec</t>
+          <t>RT_ms</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reaction time in seconds</t>
+          <t>Reaction time in milliseconds</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -793,20 +793,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>RT_sec</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Reaction time in seconds</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>ACC</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Accuracy of the response</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>0;1</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Numerical</t>
         </is>
